--- a/my-app/public/masterbudget.xlsx
+++ b/my-app/public/masterbudget.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryantarapchak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CED80607-8F82-934E-9F04-441789D9EDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{896A424B-8C63-0E44-BB51-97073F94DBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="15880" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Income Statement" sheetId="11" r:id="rId11"/>
     <sheet name="Statement of Retained Earnings" sheetId="15" r:id="rId12"/>
     <sheet name="Closing Balance Sheet" sheetId="13" r:id="rId13"/>
-    <sheet name="Cash Flow Statement" sheetId="14" r:id="rId14"/>
+    <sheet name="Statement of Cash Flows" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -459,7 +459,7 @@
     <t>Closing Balance Sheet</t>
   </si>
   <si>
-    <t>Cash Flow Statement</t>
+    <t>Statement of Cash Flows</t>
   </si>
 </sst>
 </file>
@@ -599,13 +599,13 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -920,10 +920,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -1194,19 +1194,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -1448,18 +1448,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -1706,13 +1706,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -1829,10 +1829,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
@@ -1963,15 +1963,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -2133,13 +2133,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -2247,16 +2247,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2464,17 +2464,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -2678,18 +2678,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -2914,19 +2914,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -3164,15 +3164,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -3329,15 +3329,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -3500,14 +3500,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
